--- a/attendance_demo_IT_2026_06_chinh_lai.xlsx
+++ b/attendance_demo_IT_2026_06_chinh_lai.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\SWP_GROUP2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC015345-3A0B-4C45-A7DA-DE0FBBFC7F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE78E0B-3089-4FF4-B788-D108FBF6DCFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
   <si>
     <t>fullName</t>
   </si>
@@ -47,12 +47,6 @@
     <t>timeOut</t>
   </si>
   <si>
-    <t>attendanceStatus</t>
-  </si>
-  <si>
-    <t>note</t>
-  </si>
-  <si>
     <t>EMP001</t>
   </si>
   <si>
@@ -71,9 +65,6 @@
     <t>17:00</t>
   </si>
   <si>
-    <t>PRESENT</t>
-  </si>
-  <si>
     <t>2026-06-02</t>
   </si>
   <si>
@@ -83,12 +74,6 @@
     <t>17:05</t>
   </si>
   <si>
-    <t>LATE</t>
-  </si>
-  <si>
-    <t>Đi trễ</t>
-  </si>
-  <si>
     <t>EMP002</t>
   </si>
   <si>
@@ -98,12 +83,6 @@
     <t>17:30</t>
   </si>
   <si>
-    <t>ABSENT</t>
-  </si>
-  <si>
-    <t>Nghỉ phép</t>
-  </si>
-  <si>
     <t>EMP003</t>
   </si>
   <si>
@@ -114,12 +93,6 @@
   </si>
   <si>
     <t>18:00</t>
-  </si>
-  <si>
-    <t>UNEXCUSED</t>
-  </si>
-  <si>
-    <t>Nghỉ không phép</t>
   </si>
   <si>
     <t>employeeCode</t>
@@ -185,66 +158,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF4C1130"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFEADCF8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF990000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF274E13"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFD9EAD3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -258,16 +184,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{85B5E18B-CAB5-4823-99C1-62D055E95F38}" name="Attendance_HR_Table3" displayName="Attendance_HR_Table3" ref="A1:H7">
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{85B5E18B-CAB5-4823-99C1-62D055E95F38}" name="Attendance_HR_Table3" displayName="Attendance_HR_Table3" ref="A1:F7">
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{18988C59-3DCC-46E7-AE13-26D312FC0130}" name="employeeCode"/>
     <tableColumn id="7" xr3:uid="{126C0934-640C-476C-A9F9-D0CD303C6055}" name="fullName"/>
     <tableColumn id="8" xr3:uid="{61803E49-EC6C-4C24-B06C-748D8278F76E}" name="Department"/>
     <tableColumn id="2" xr3:uid="{2BEB1EA3-E873-4C1C-84A2-6A8E5AC2F110}" name="workDate"/>
     <tableColumn id="3" xr3:uid="{00BA6287-41AB-40E1-9606-3FF73EC21B3E}" name="timeIn"/>
     <tableColumn id="4" xr3:uid="{591DCB47-99DA-4949-9EF6-ECE062C970F6}" name="timeOut"/>
-    <tableColumn id="5" xr3:uid="{0FFB0C97-A9A8-4A12-B4E5-51C065BDD64A}" name="attendanceStatus"/>
-    <tableColumn id="6" xr3:uid="{62A0194E-24CC-4D94-BD16-BB8310A04B7E}" name="note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -558,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" customWidth="1"/>
@@ -570,15 +494,15 @@
     <col min="8" max="8" width="16.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>30</v>
+      <c r="C1" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -589,169 +513,117 @@
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="H3" t="s">
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
         <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G7">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>G2="PRESENT"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
-      <formula>G2="LATE"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>G2="ABSENT"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4">
-      <formula>G2="UNEXCUSED"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="G2:G7" xr:uid="{5FEC58C1-C630-4A4F-B99D-7034BC1A142F}">
-      <formula1>"PRESENT,LATE,ABSENT,UNEXCUSED"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
